--- a/Data_clean/MCAS/Estados_US/Edos_USA_2017/RHODE_ISLAND_2017.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2017/RHODE_ISLAND_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C3">
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -460,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -473,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -486,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -499,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -530,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -543,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -556,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -569,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -582,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -595,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -608,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -623,12 +703,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C20">
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Papalotla</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -685,7 +780,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C24">
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -755,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C29">
@@ -766,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C30">
@@ -779,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C31">
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -805,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C33">
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -831,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C35">
@@ -844,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C36">
@@ -857,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C37">
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -922,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C42">
@@ -935,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C43">
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -1018,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huasca de Ocampo</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C49">
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -1044,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1057,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C52">
@@ -1070,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tlahuelilpan</t>
@@ -1083,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -1096,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tlaxcoapan</t>
@@ -1109,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1122,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1153,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C59">
@@ -1166,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C60">
@@ -1179,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -1192,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C62">
@@ -1205,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1236,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1275,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1288,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Nahuatzen</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -1327,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1340,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1371,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -1384,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1446,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -1459,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>San Dionisio del Mar</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C81">
@@ -1472,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -1485,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1498,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -1511,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -1524,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1555,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -1568,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -1581,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -1594,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1607,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1620,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C93">
@@ -1633,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -1646,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1659,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>San Nicolás de los Ranchos</t>
+          <t>San Nicolás De Los Ranchos</t>
         </is>
       </c>
       <c r="C96">
@@ -1672,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -1685,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1698,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -1711,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -1724,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -1737,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1750,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Xicotlán</t>
@@ -1763,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1783,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C105">
@@ -1794,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C106">
@@ -1807,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C107">
@@ -1820,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1851,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -1864,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C111">
@@ -1877,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1908,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -1921,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1952,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1983,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -1996,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2027,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -2040,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Chiconamel</t>
@@ -2053,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2066,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -2079,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -2092,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2105,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -2118,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -2131,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -2144,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -2157,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C132">
@@ -2170,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -2183,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -2196,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2209,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2222,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2253,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2284,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2307,76 +2907,6 @@
       </c>
       <c r="D142">
         <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
